--- a/Dashboard de Vendas do Xbox com Excel.xlsx
+++ b/Dashboard de Vendas do Xbox com Excel.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruna\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e29fb2d12606b095/Área de Trabalho/Projetos/Excel/Dashboard de Vendas do Xbox com Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE618827-81E8-4F2D-9A0F-2EFEC5CCFA26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{BE618827-81E8-4F2D-9A0F-2EFEC5CCFA26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52E63C1D-7158-4BD9-92A8-A16BC262F089}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="517" firstSheet="3" activeTab="3" xr2:uid="{28DD5B76-0634-4F87-BE60-8BFA7EF2E23B}"/>
   </bookViews>
@@ -30,7 +30,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="14" r:id="rId7"/>
+    <pivotCache cacheId="0" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2023" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2023" uniqueCount="325">
   <si>
     <t>Paleta de Cores</t>
   </si>
@@ -1117,9 +1117,6 @@
     <t>Pergunta Negócio 3 - Total de Vendas de Assinaturas do EA Play</t>
   </si>
   <si>
-    <t>(Tudo)</t>
-  </si>
-  <si>
     <t>Pergunta Negócio 4 - Total de Vendas de Assinaturas do Minecraft Season Pass</t>
   </si>
   <si>
@@ -1135,7 +1132,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -1313,11 +1310,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -1328,6 +1321,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Moeda" xfId="2" builtinId="4"/>
@@ -1336,38 +1333,6 @@
     <cellStyle name="Título 1" xfId="1" builtinId="16"/>
   </cellStyles>
   <dxfs count="16">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF22C55E"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1410,11 +1375,43 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF22C55E"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="SlicerStyleLight6 2" pivot="0" table="0" count="10" xr9:uid="{608F4308-4995-4978-9FC1-8A210DD35A33}">
-      <tableStyleElement type="wholeTable" dxfId="1"/>
-      <tableStyleElement type="headerRow" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="15"/>
+      <tableStyleElement type="headerRow" dxfId="14"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -3654,8 +3651,8 @@
       <xdr:row>14</xdr:row>
       <xdr:rowOff>53340</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="7" name="Subscription Type">
@@ -3678,7 +3675,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -3907,7 +3904,8 @@
                 </a:solidFill>
                 <a:latin typeface="Aptos Narrow"/>
               </a:rPr>
-              <a:t>R$ 2.940,00</a:t>
+              <a:pPr algn="ctr"/>
+              <a:t>R$ 990,00</a:t>
             </a:fld>
             <a:endParaRPr lang="pt-BR" sz="3200" kern="1200">
               <a:solidFill>
@@ -4420,7 +4418,8 @@
                 </a:solidFill>
                 <a:latin typeface="Aptos Narrow"/>
               </a:rPr>
-              <a:t>R$ 3.880,00</a:t>
+              <a:pPr algn="ctr"/>
+              <a:t>R$ 1.140,00</a:t>
             </a:fld>
             <a:endParaRPr lang="pt-BR" sz="3200" kern="1200">
               <a:solidFill>
@@ -4802,12 +4801,14 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="TITULAR"/>
       <sheetName val="INFORMES"/>
       <sheetName val="NOTAS"/>
       <sheetName val="TABELAS"/>
+      <sheetName val="Organizador de Declaração de Im"/>
     </sheetNames>
     <definedNames>
       <definedName name="MoverIconeParaPosicao"/>
@@ -4817,6 +4818,7 @@
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
+      <sheetData sheetId="4" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -9318,147 +9320,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7976CC6A-72F6-48F1-B5D8-D8ED299236ED}" name="Tabela dinâmica4" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="B29:C33" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="13">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="44" showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="6" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Soma de Minecraft Season Pass Price" fld="10" baseField="0" baseItem="0" numFmtId="44"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{000B9855-DA08-403B-9B9C-2C34A5B33842}" name="tbl_easeasonpass_total" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="B19:C23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="13">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-    <pivotField numFmtId="44" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="6" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Soma de EA Play Season Pass" fld="8" baseField="2" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0411CA0C-654D-4207-ADFD-05DEDAD5B9D8}" name="tbl_annual_total" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0411CA0C-654D-4207-ADFD-05DEDAD5B9D8}" name="tbl_annual_total" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="B10:C13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="13">
     <pivotField showAll="0"/>
@@ -9475,8 +9337,8 @@
     <pivotField numFmtId="44" showAll="0"/>
     <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
       <items count="4">
-        <item x="1"/>
-        <item x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" x="0"/>
         <item x="2"/>
         <item t="default"/>
       </items>
@@ -9534,6 +9396,146 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7976CC6A-72F6-48F1-B5D8-D8ED299236ED}" name="Tabela dinâmica4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="B29:C33" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="13">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="4">
+        <item h="1" x="1"/>
+        <item h="1" x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="6" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Soma de Minecraft Season Pass Price" fld="10" baseField="0" baseItem="0" numFmtId="44"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{000B9855-DA08-403B-9B9C-2C34A5B33842}" name="tbl_easeasonpass_total" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="B19:C23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="13">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="4">
+        <item h="1" x="1"/>
+        <item h="1" x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="6" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Soma de EA Play Season Pass" fld="8" baseField="2" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="SegmentaçãodeDados_Subscription_Type" xr10:uid="{592DF776-E343-4598-975F-F248CF730C9E}" sourceName="Subscription Type">
   <pivotTables>
@@ -9544,8 +9546,8 @@
   <data>
     <tabular pivotCacheId="1244597137">
       <items count="3">
-        <i x="1" s="1"/>
-        <i x="0" s="1"/>
+        <i x="1"/>
+        <i x="0"/>
         <i x="2" s="1"/>
       </items>
     </tabular>
@@ -9560,7 +9562,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34E0E886-4200-4B36-97B3-63DB74FF40A0}" name="Tabela1" displayName="Tabela1" ref="A1:M296" totalsRowShown="0" dataDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34E0E886-4200-4B36-97B3-63DB74FF40A0}" name="Tabela1" displayName="Tabela1" ref="A1:M296" totalsRowShown="0" dataDxfId="13">
   <autoFilter ref="A1:M296" xr:uid="{34E0E886-4200-4B36-97B3-63DB74FF40A0}">
     <filterColumn colId="7">
       <filters>
@@ -9569,19 +9571,19 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{C4A90516-688A-46BF-9167-EA16C2A8A652}" name="Subscriber ID" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{53DD39D0-2220-4121-9E9D-4EAA7E151C0F}" name="Name" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{4F5FF271-4C57-4BE0-8F2C-F82C8551625C}" name="Plan" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{8C17EB93-79B9-4E55-B8F7-BEB82F8253E9}" name="Start Date" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{48CEDF9B-1689-482A-A828-5CCE7713264A}" name="Auto Renewal" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{78B82374-9AA7-4E38-AE4F-78CDE6C83720}" name="Subscription Price" dataDxfId="9" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{F2433F68-AF33-49D0-B1FB-19A396074EDE}" name="Subscription Type" dataDxfId="8"/>
-    <tableColumn id="8" xr3:uid="{FD4D9C95-F6E5-4933-9068-A71FF7DF9343}" name="EA Play Season Pass" dataDxfId="7"/>
-    <tableColumn id="13" xr3:uid="{978DD0D2-834E-4CE4-A39B-30976086932F}" name="EA Play Season Pass_x000a_Price" dataDxfId="6" dataCellStyle="Moeda"/>
-    <tableColumn id="9" xr3:uid="{6E29F111-C395-4580-9DAD-3407D9E8B1A4}" name="Minecraft Season Pass" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{EF544EAA-7F25-4FD5-A10E-8E62804DB9E3}" name="Minecraft Season Pass Price" dataDxfId="4" dataCellStyle="Moeda"/>
-    <tableColumn id="11" xr3:uid="{7F6EB64A-1F07-4E48-9F0F-AC7D9DCD26F8}" name="Coupon Value" dataDxfId="3" dataCellStyle="Moeda"/>
-    <tableColumn id="12" xr3:uid="{2B04ABC8-DE6F-426E-ADC0-D8AFC68CA58E}" name="Total Value" dataDxfId="2" dataCellStyle="Moeda"/>
+    <tableColumn id="1" xr3:uid="{C4A90516-688A-46BF-9167-EA16C2A8A652}" name="Subscriber ID" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{53DD39D0-2220-4121-9E9D-4EAA7E151C0F}" name="Name" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{4F5FF271-4C57-4BE0-8F2C-F82C8551625C}" name="Plan" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{8C17EB93-79B9-4E55-B8F7-BEB82F8253E9}" name="Start Date" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{48CEDF9B-1689-482A-A828-5CCE7713264A}" name="Auto Renewal" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{78B82374-9AA7-4E38-AE4F-78CDE6C83720}" name="Subscription Price" dataDxfId="7" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{F2433F68-AF33-49D0-B1FB-19A396074EDE}" name="Subscription Type" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{FD4D9C95-F6E5-4933-9068-A71FF7DF9343}" name="EA Play Season Pass" dataDxfId="5"/>
+    <tableColumn id="13" xr3:uid="{978DD0D2-834E-4CE4-A39B-30976086932F}" name="EA Play Season Pass_x000a_Price" dataDxfId="4" dataCellStyle="Moeda"/>
+    <tableColumn id="9" xr3:uid="{6E29F111-C395-4580-9DAD-3407D9E8B1A4}" name="Minecraft Season Pass" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{EF544EAA-7F25-4FD5-A10E-8E62804DB9E3}" name="Minecraft Season Pass Price" dataDxfId="2" dataCellStyle="Moeda"/>
+    <tableColumn id="11" xr3:uid="{7F6EB64A-1F07-4E48-9F0F-AC7D9DCD26F8}" name="Coupon Value" dataDxfId="1" dataCellStyle="Moeda"/>
+    <tableColumn id="12" xr3:uid="{2B04ABC8-DE6F-426E-ADC0-D8AFC68CA58E}" name="Total Value" dataDxfId="0" dataCellStyle="Moeda"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -22261,13 +22263,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="22" t="s">
         <v>313</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
@@ -22284,7 +22286,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>322</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
@@ -22300,7 +22302,7 @@
         <v>23</v>
       </c>
       <c r="C11" s="13">
-        <v>3847</v>
+        <v>806</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
@@ -22308,7 +22310,7 @@
         <v>19</v>
       </c>
       <c r="C12" s="13">
-        <v>3786</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
@@ -22316,7 +22318,7 @@
         <v>318</v>
       </c>
       <c r="C13" s="13">
-        <v>7633</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.3">
@@ -22329,7 +22331,7 @@
         <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>322</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
@@ -22344,7 +22346,7 @@
       <c r="B20" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="18">
+      <c r="C20" s="23">
         <v>0</v>
       </c>
     </row>
@@ -22352,7 +22354,7 @@
       <c r="B21" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="18">
+      <c r="C21" s="23">
         <v>0</v>
       </c>
     </row>
@@ -22360,26 +22362,26 @@
       <c r="B22" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="18">
-        <v>2940</v>
+      <c r="C22" s="23">
+        <v>990</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="12" t="s">
         <v>318</v>
       </c>
-      <c r="C23" s="18">
-        <v>2940</v>
-      </c>
-      <c r="E23" s="19">
+      <c r="C23" s="23">
+        <v>990</v>
+      </c>
+      <c r="E23" s="18">
         <f>GETPIVOTDATA("EA Play Season Pass
 Price",$B$19)</f>
-        <v>2940</v>
+        <v>990</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="12" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.3">
@@ -22387,7 +22389,7 @@
         <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>322</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
@@ -22395,7 +22397,7 @@
         <v>316</v>
       </c>
       <c r="C29" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.3">
@@ -22411,7 +22413,7 @@
         <v>26</v>
       </c>
       <c r="C31" s="13">
-        <v>1920</v>
+        <v>480</v>
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.3">
@@ -22419,7 +22421,7 @@
         <v>18</v>
       </c>
       <c r="C32" s="13">
-        <v>1960</v>
+        <v>660</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.3">
@@ -22427,11 +22429,11 @@
         <v>318</v>
       </c>
       <c r="C33" s="13">
-        <v>3880</v>
-      </c>
-      <c r="E33" s="19">
+        <v>1140</v>
+      </c>
+      <c r="E33" s="18">
         <f>GETPIVOTDATA("Minecraft Season Pass Price",$B$29)</f>
-        <v>3880</v>
+        <v>1140</v>
       </c>
     </row>
   </sheetData>
@@ -22448,16 +22450,16 @@
   <dimension ref="A1:Q35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.44140625" style="23" customWidth="1"/>
+    <col min="1" max="1" width="27.44140625" style="21" customWidth="1"/>
     <col min="2" max="2" width="3.5546875" customWidth="1"/>
     <col min="12" max="12" width="6.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A1" s="21"/>
+      <c r="A1" s="19"/>
     </row>
     <row r="2" spans="1:17" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A2" s="21"/>
+      <c r="A2" s="19"/>
       <c r="C2" s="15" t="s">
         <v>319</v>
       </c>
@@ -22477,10 +22479,10 @@
       <c r="Q2" s="16"/>
     </row>
     <row r="3" spans="1:17" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="21"/>
+      <c r="A3" s="19"/>
     </row>
     <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="21"/>
+      <c r="A4" s="19"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
@@ -22499,8 +22501,8 @@
       <c r="Q4" s="7"/>
     </row>
     <row r="5" spans="1:17" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="22" t="s">
-        <v>325</v>
+      <c r="A5" s="20" t="s">
+        <v>324</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -22520,7 +22522,7 @@
       <c r="Q5" s="7"/>
     </row>
     <row r="6" spans="1:17" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="21"/>
+      <c r="A6" s="19"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -22539,7 +22541,7 @@
       <c r="Q6" s="7"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="21"/>
+      <c r="A7" s="19"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
@@ -22558,7 +22560,7 @@
       <c r="Q7" s="7"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="21"/>
+      <c r="A8" s="19"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -22577,7 +22579,7 @@
       <c r="Q8" s="7"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="21"/>
+      <c r="A9" s="19"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -22596,7 +22598,7 @@
       <c r="Q9" s="7"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="21"/>
+      <c r="A10" s="19"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -22615,7 +22617,7 @@
       <c r="Q10" s="7"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="21"/>
+      <c r="A11" s="19"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -22634,7 +22636,7 @@
       <c r="Q11" s="7"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="21"/>
+      <c r="A12" s="19"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -22653,7 +22655,7 @@
       <c r="Q12" s="7"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="21"/>
+      <c r="A13" s="19"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -22672,7 +22674,7 @@
       <c r="Q13" s="7"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A14" s="21"/>
+      <c r="A14" s="19"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -22691,7 +22693,7 @@
       <c r="Q14" s="7"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15" s="21"/>
+      <c r="A15" s="19"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -22710,7 +22712,7 @@
       <c r="Q15" s="7"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A16" s="21"/>
+      <c r="A16" s="19"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
@@ -22729,7 +22731,7 @@
       <c r="Q16" s="7"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A17" s="21"/>
+      <c r="A17" s="19"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
@@ -22748,7 +22750,7 @@
       <c r="Q17" s="7"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A18" s="21"/>
+      <c r="A18" s="19"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
@@ -22767,7 +22769,7 @@
       <c r="Q18" s="7"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A19" s="21"/>
+      <c r="A19" s="19"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
@@ -22786,7 +22788,7 @@
       <c r="Q19" s="7"/>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A20" s="21"/>
+      <c r="A20" s="19"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
@@ -22805,7 +22807,7 @@
       <c r="Q20" s="7"/>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A21" s="21"/>
+      <c r="A21" s="19"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
@@ -22824,7 +22826,7 @@
       <c r="Q21" s="7"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A22" s="21"/>
+      <c r="A22" s="19"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
@@ -22843,7 +22845,7 @@
       <c r="Q22" s="7"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A23" s="21"/>
+      <c r="A23" s="19"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
@@ -22862,7 +22864,7 @@
       <c r="Q23" s="7"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A24" s="21"/>
+      <c r="A24" s="19"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
@@ -22881,7 +22883,7 @@
       <c r="Q24" s="7"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A25" s="21"/>
+      <c r="A25" s="19"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
@@ -22900,7 +22902,7 @@
       <c r="Q25" s="7"/>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A26" s="21"/>
+      <c r="A26" s="19"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
@@ -22919,7 +22921,7 @@
       <c r="Q26" s="7"/>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A27" s="21"/>
+      <c r="A27" s="19"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
@@ -22938,7 +22940,7 @@
       <c r="Q27" s="7"/>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A28" s="21"/>
+      <c r="A28" s="19"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
@@ -22957,7 +22959,7 @@
       <c r="Q28" s="7"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A29" s="21"/>
+      <c r="A29" s="19"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
@@ -22976,7 +22978,7 @@
       <c r="Q29" s="7"/>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A30" s="21"/>
+      <c r="A30" s="19"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
@@ -22995,7 +22997,7 @@
       <c r="Q30" s="7"/>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A31" s="21"/>
+      <c r="A31" s="19"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
@@ -23014,7 +23016,7 @@
       <c r="Q31" s="7"/>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A32" s="21"/>
+      <c r="A32" s="19"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
@@ -23033,7 +23035,7 @@
       <c r="Q32" s="7"/>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A33" s="21"/>
+      <c r="A33" s="19"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
@@ -23052,7 +23054,7 @@
       <c r="Q33" s="7"/>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A34" s="21"/>
+      <c r="A34" s="19"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
@@ -23071,7 +23073,7 @@
       <c r="Q34" s="7"/>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A35" s="21"/>
+      <c r="A35" s="19"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
@@ -23104,26 +23106,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="851b35d3-0456-4d6a-bc2f-da927e91d158">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="19483571-f922-4e8e-9c1c-26f0a2252132" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010001E48B58A68BE64E9120D347E3E06B3A" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="2f90046ec77328b7f86417d2e03b3d33">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="851b35d3-0456-4d6a-bc2f-da927e91d158" xmlns:ns3="19483571-f922-4e8e-9c1c-26f0a2252132" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c815006ac2d4f05ee97fdd57e40d8e38" ns2:_="" ns3:_="">
     <xsd:import namespace="851b35d3-0456-4d6a-bc2f-da927e91d158"/>
@@ -23378,26 +23360,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFD3D529-BCD3-4ECD-9B2A-42924892FFCB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="851b35d3-0456-4d6a-bc2f-da927e91d158"/>
-    <ds:schemaRef ds:uri="19483571-f922-4e8e-9c1c-26f0a2252132"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3B4D9D5-B351-46EB-A728-C3362FE437D4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="851b35d3-0456-4d6a-bc2f-da927e91d158">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="19483571-f922-4e8e-9c1c-26f0a2252132" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32608D25-EC36-42FE-A1DC-F778995A6799}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -23414,4 +23397,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3B4D9D5-B351-46EB-A728-C3362FE437D4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFD3D529-BCD3-4ECD-9B2A-42924892FFCB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="851b35d3-0456-4d6a-bc2f-da927e91d158"/>
+    <ds:schemaRef ds:uri="19483571-f922-4e8e-9c1c-26f0a2252132"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>